--- a/data/Formula_1/Formula_1.xlsx
+++ b/data/Formula_1/Formula_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vyan\Documents\GitHub\Formula_1\data\Formula_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94FD563-71ED-47BA-B0F4-37EF802B5338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38265FB3-C1B3-4229-A2D0-956DF1FE1822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="584" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="584" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Drivers" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="186">
   <si>
     <t>Name</t>
   </si>
@@ -582,6 +582,45 @@
   </si>
   <si>
     <t>🇳🇱 Netherlands</t>
+  </si>
+  <si>
+    <t>DNS</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>RET</t>
+  </si>
+  <si>
+    <t>+2.974s</t>
+  </si>
+  <si>
+    <t>+15.519s</t>
+  </si>
+  <si>
+    <t>+16.144s</t>
+  </si>
+  <si>
+    <t>+51.741s</t>
+  </si>
+  <si>
+    <t>+54.617s</t>
+  </si>
+  <si>
+    <t>+1 lap</t>
+  </si>
+  <si>
+    <t>+2 laps</t>
+  </si>
+  <si>
+    <t>+3 laps</t>
+  </si>
+  <si>
+    <t>+15 laps</t>
+  </si>
+  <si>
+    <t>DNF</t>
   </si>
 </sst>
 </file>
@@ -681,7 +720,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -720,9 +759,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -756,33 +792,30 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="47" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="110">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -806,6 +839,7 @@
           <bgColor theme="1" tint="0.14999847407452621"/>
         </patternFill>
       </fill>
+      <alignment horizontal="right" vertical="center" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -854,560 +888,16 @@
           <bgColor theme="1" tint="0.14999847407452621"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill>
           <fgColor indexed="64"/>
           <bgColor theme="1" tint="0.14999847407452621"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1437,11 +927,294 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1461,6 +1234,1079 @@
         <scheme val="minor"/>
       </font>
       <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="90" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="90" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill>
+          <fgColor indexed="64"/>
+          <bgColor theme="1" tint="0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
         <patternFill>
           <fgColor indexed="64"/>
           <bgColor theme="1" tint="0.14999847407452621"/>
@@ -1491,795 +2337,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="90" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="90" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="90" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="1" tint="0.14999847407452621"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4106,164 +4163,164 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4B171726-5CF9-40B3-94E6-B2AFCA2134DB}" name="Table3" displayName="Table3" ref="B1:F23" totalsRowShown="0" headerRowDxfId="109" dataDxfId="108">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4B171726-5CF9-40B3-94E6-B2AFCA2134DB}" name="Table3" displayName="Table3" ref="B1:F23" totalsRowShown="0" headerRowDxfId="84" dataDxfId="83">
   <autoFilter ref="B1:F23" xr:uid="{4B171726-5CF9-40B3-94E6-B2AFCA2134DB}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{92146AF8-CFF9-4D3A-91B4-9CC9F7F0289D}" name="Name" dataDxfId="107"/>
-    <tableColumn id="2" xr3:uid="{7EE4C027-225E-49B2-8B95-07D077269830}" name="Team" dataDxfId="106"/>
-    <tableColumn id="3" xr3:uid="{EB96D9FA-7CEA-42EF-ABF7-51E4E7D01475}" name="Number" dataDxfId="105"/>
-    <tableColumn id="4" xr3:uid="{98E1A7EE-661C-45CE-822E-9854C47706AF}" name="Country" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{DB605153-3E17-4802-AB05-2429688C9895}" name="Constructor" dataDxfId="104"/>
+    <tableColumn id="1" xr3:uid="{92146AF8-CFF9-4D3A-91B4-9CC9F7F0289D}" name="Name" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{7EE4C027-225E-49B2-8B95-07D077269830}" name="Team" dataDxfId="81"/>
+    <tableColumn id="3" xr3:uid="{EB96D9FA-7CEA-42EF-ABF7-51E4E7D01475}" name="Number" dataDxfId="80"/>
+    <tableColumn id="4" xr3:uid="{98E1A7EE-661C-45CE-822E-9854C47706AF}" name="Country" dataDxfId="79"/>
+    <tableColumn id="5" xr3:uid="{DB605153-3E17-4802-AB05-2429688C9895}" name="Constructor" dataDxfId="78"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{628F433B-E56B-4D70-88FE-7F39124D9319}" name="Table1" displayName="Table1" ref="B2:J26" totalsRowShown="0" headerRowDxfId="103" dataDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{628F433B-E56B-4D70-88FE-7F39124D9319}" name="Table1" displayName="Table1" ref="B2:J26" totalsRowShown="0" headerRowDxfId="77" dataDxfId="76">
   <autoFilter ref="B2:J26" xr:uid="{628F433B-E56B-4D70-88FE-7F39124D9319}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{6FFFFB14-66EC-4894-BC5C-904E91719C15}" name="Race Name" dataDxfId="101"/>
-    <tableColumn id="2" xr3:uid="{A2C1729C-5A9F-4F3B-9D25-29460232C8BB}" name="Circuit Name" dataDxfId="100"/>
-    <tableColumn id="3" xr3:uid="{CDE8E4A3-91F0-42E8-9535-50FE31EF16BE}" name="Location" dataDxfId="99"/>
-    <tableColumn id="4" xr3:uid="{15A0D957-CB98-4793-9130-02DA6096C7EE}" name="Race Date" dataDxfId="98"/>
-    <tableColumn id="5" xr3:uid="{5C322528-271F-4EDD-8D7B-6FAE995790B5}" name="Distance" dataDxfId="97"/>
-    <tableColumn id="6" xr3:uid="{E39D53C2-53BA-4179-9C6E-AD4D5427D7C5}" name="Fastest Time" dataDxfId="96"/>
-    <tableColumn id="7" xr3:uid="{61ABA8A6-ABC2-4008-93AA-C07FC2524B57}" name="1" dataDxfId="95"/>
-    <tableColumn id="8" xr3:uid="{91B3BA5A-8F2D-45BB-B42E-FCE1231D8296}" name="2" dataDxfId="94"/>
-    <tableColumn id="9" xr3:uid="{208C354C-D504-490A-9A6E-F1C70382A1BD}" name="3" dataDxfId="93"/>
+    <tableColumn id="1" xr3:uid="{6FFFFB14-66EC-4894-BC5C-904E91719C15}" name="Race Name" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{A2C1729C-5A9F-4F3B-9D25-29460232C8BB}" name="Circuit Name" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{CDE8E4A3-91F0-42E8-9535-50FE31EF16BE}" name="Location" dataDxfId="73"/>
+    <tableColumn id="4" xr3:uid="{15A0D957-CB98-4793-9130-02DA6096C7EE}" name="Race Date" dataDxfId="72"/>
+    <tableColumn id="5" xr3:uid="{5C322528-271F-4EDD-8D7B-6FAE995790B5}" name="Distance" dataDxfId="71"/>
+    <tableColumn id="6" xr3:uid="{E39D53C2-53BA-4179-9C6E-AD4D5427D7C5}" name="Fastest Time" dataDxfId="70"/>
+    <tableColumn id="7" xr3:uid="{61ABA8A6-ABC2-4008-93AA-C07FC2524B57}" name="1" dataDxfId="69"/>
+    <tableColumn id="8" xr3:uid="{91B3BA5A-8F2D-45BB-B42E-FCE1231D8296}" name="2" dataDxfId="68"/>
+    <tableColumn id="9" xr3:uid="{208C354C-D504-490A-9A6E-F1C70382A1BD}" name="3" dataDxfId="67"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9C9B7447-5CAF-49A8-849A-24FFEF88E594}" name="Table4" displayName="Table4" ref="A1:Y48" totalsRowShown="0" headerRowDxfId="92" dataDxfId="91">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9C9B7447-5CAF-49A8-849A-24FFEF88E594}" name="Table4" displayName="Table4" ref="A1:Y48" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
   <autoFilter ref="A1:Y48" xr:uid="{9C9B7447-5CAF-49A8-849A-24FFEF88E594}"/>
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{CF33613A-B550-44CB-881B-6F14CACD5B72}" name="Driver" dataDxfId="90"/>
-    <tableColumn id="3" xr3:uid="{64862BF4-56F0-4709-A8AB-C085BAF0215A}" name="Australian Grand Prix" dataDxfId="89"/>
-    <tableColumn id="4" xr3:uid="{2D3377A0-58D7-467A-99BD-8DD5E5195992}" name="Chinese Grand Prix" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{0ECE7874-3069-4E86-A858-526B2561A56E}" name="Japanese Grand Prix" dataDxfId="87"/>
-    <tableColumn id="6" xr3:uid="{3332362F-E796-4D76-B72D-D37A9E8C4506}" name="Bahrain Grand Prix" dataDxfId="86"/>
-    <tableColumn id="7" xr3:uid="{6A873417-5AFE-4D0F-88A9-6011AD971FED}" name="Saudi Arabian Grand Prix" dataDxfId="85"/>
-    <tableColumn id="8" xr3:uid="{2384B2F0-E1B8-4D15-A86A-C506AC2DDE75}" name="Miami Grand Prix" dataDxfId="84"/>
-    <tableColumn id="9" xr3:uid="{A4F6721E-F16D-4038-BD64-3E8A7D38B02F}" name="Emilia Romagna Grand Prix" dataDxfId="83"/>
-    <tableColumn id="10" xr3:uid="{435C1CC1-7C35-4D05-B75A-E2D3EA9487F5}" name="Monaco Grand Prix" dataDxfId="82"/>
-    <tableColumn id="11" xr3:uid="{7324DE86-EE77-4D97-944F-558B5246B501}" name="Spanish Grand Prix" dataDxfId="81"/>
-    <tableColumn id="12" xr3:uid="{B0654BA4-C5FE-40FC-94D4-F2829B439C83}" name="Canadian Grand Prix" dataDxfId="80"/>
-    <tableColumn id="13" xr3:uid="{40A2DB89-A1EF-4668-BB5F-0C8F41981CE9}" name="Austrian Grand Prix" dataDxfId="79"/>
-    <tableColumn id="14" xr3:uid="{7E4C0B80-60BB-443B-B58C-2C484E838E2D}" name="British Grand Prix" dataDxfId="78"/>
-    <tableColumn id="15" xr3:uid="{D7685E94-DED7-4922-8549-80717F6854B8}" name="Belgian Grand Prix" dataDxfId="77"/>
-    <tableColumn id="16" xr3:uid="{E8B67644-354D-4320-AEE9-C7236B9F7A62}" name="Hungarian Grand Prix" dataDxfId="76"/>
-    <tableColumn id="17" xr3:uid="{9744C7B8-818D-4DE8-B37D-EFBCC20F2D87}" name="Dutch Grand Prix" dataDxfId="75"/>
-    <tableColumn id="18" xr3:uid="{EF67C45C-CAC1-4298-A58A-EEA09E9B8331}" name="Italian Grand Prix" dataDxfId="74"/>
-    <tableColumn id="19" xr3:uid="{298F9D14-379A-45B8-8779-FD50639B978E}" name="Azerbaijan Grand Prix" dataDxfId="73"/>
-    <tableColumn id="20" xr3:uid="{A88F8700-7FAE-4431-8633-EE182CD448DA}" name="Singapore Grand Prix" dataDxfId="72"/>
-    <tableColumn id="21" xr3:uid="{EDA628AE-0844-4D1C-9A31-622106A74B74}" name="United States Grand Prix" dataDxfId="71"/>
-    <tableColumn id="22" xr3:uid="{40DA2915-5603-475B-B8B3-83784AE5046E}" name="Mexico City Grand Prix" dataDxfId="70"/>
-    <tableColumn id="23" xr3:uid="{46622AFA-DB78-4AE5-89D9-F1D3556D5A3D}" name="São Paulo Grand Prix" dataDxfId="69"/>
-    <tableColumn id="24" xr3:uid="{3EC53053-E45B-44EE-AC6B-F7BB5EB7B9F5}" name="Las Vegas Grand Prix" dataDxfId="68"/>
-    <tableColumn id="25" xr3:uid="{6F3819A8-BF88-4B0C-9F74-4EE092BA245E}" name="Qatar Grand Prix" dataDxfId="67"/>
-    <tableColumn id="26" xr3:uid="{6A29A013-FF84-400E-8F74-E5A850484E6D}" name="Abu Dhabi Grand Prix" dataDxfId="66"/>
+    <tableColumn id="1" xr3:uid="{CF33613A-B550-44CB-881B-6F14CACD5B72}" name="Driver" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{64862BF4-56F0-4709-A8AB-C085BAF0215A}" name="Australian Grand Prix" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{2D3377A0-58D7-467A-99BD-8DD5E5195992}" name="Chinese Grand Prix" dataDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{0ECE7874-3069-4E86-A858-526B2561A56E}" name="Japanese Grand Prix" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{3332362F-E796-4D76-B72D-D37A9E8C4506}" name="Bahrain Grand Prix" dataDxfId="60"/>
+    <tableColumn id="7" xr3:uid="{6A873417-5AFE-4D0F-88A9-6011AD971FED}" name="Saudi Arabian Grand Prix" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{2384B2F0-E1B8-4D15-A86A-C506AC2DDE75}" name="Miami Grand Prix" dataDxfId="58"/>
+    <tableColumn id="9" xr3:uid="{A4F6721E-F16D-4038-BD64-3E8A7D38B02F}" name="Emilia Romagna Grand Prix" dataDxfId="57"/>
+    <tableColumn id="10" xr3:uid="{435C1CC1-7C35-4D05-B75A-E2D3EA9487F5}" name="Monaco Grand Prix" dataDxfId="56"/>
+    <tableColumn id="11" xr3:uid="{7324DE86-EE77-4D97-944F-558B5246B501}" name="Spanish Grand Prix" dataDxfId="55"/>
+    <tableColumn id="12" xr3:uid="{B0654BA4-C5FE-40FC-94D4-F2829B439C83}" name="Canadian Grand Prix" dataDxfId="54"/>
+    <tableColumn id="13" xr3:uid="{40A2DB89-A1EF-4668-BB5F-0C8F41981CE9}" name="Austrian Grand Prix" dataDxfId="53"/>
+    <tableColumn id="14" xr3:uid="{7E4C0B80-60BB-443B-B58C-2C484E838E2D}" name="British Grand Prix" dataDxfId="52"/>
+    <tableColumn id="15" xr3:uid="{D7685E94-DED7-4922-8549-80717F6854B8}" name="Belgian Grand Prix" dataDxfId="51"/>
+    <tableColumn id="16" xr3:uid="{E8B67644-354D-4320-AEE9-C7236B9F7A62}" name="Hungarian Grand Prix" dataDxfId="50"/>
+    <tableColumn id="17" xr3:uid="{9744C7B8-818D-4DE8-B37D-EFBCC20F2D87}" name="Dutch Grand Prix" dataDxfId="49"/>
+    <tableColumn id="18" xr3:uid="{EF67C45C-CAC1-4298-A58A-EEA09E9B8331}" name="Italian Grand Prix" dataDxfId="48"/>
+    <tableColumn id="19" xr3:uid="{298F9D14-379A-45B8-8779-FD50639B978E}" name="Azerbaijan Grand Prix" dataDxfId="47"/>
+    <tableColumn id="20" xr3:uid="{A88F8700-7FAE-4431-8633-EE182CD448DA}" name="Singapore Grand Prix" dataDxfId="46"/>
+    <tableColumn id="21" xr3:uid="{EDA628AE-0844-4D1C-9A31-622106A74B74}" name="United States Grand Prix" dataDxfId="45"/>
+    <tableColumn id="22" xr3:uid="{40DA2915-5603-475B-B8B3-83784AE5046E}" name="Mexico City Grand Prix" dataDxfId="44"/>
+    <tableColumn id="23" xr3:uid="{46622AFA-DB78-4AE5-89D9-F1D3556D5A3D}" name="São Paulo Grand Prix" dataDxfId="43"/>
+    <tableColumn id="24" xr3:uid="{3EC53053-E45B-44EE-AC6B-F7BB5EB7B9F5}" name="Las Vegas Grand Prix" dataDxfId="42"/>
+    <tableColumn id="25" xr3:uid="{6F3819A8-BF88-4B0C-9F74-4EE092BA245E}" name="Qatar Grand Prix" dataDxfId="41"/>
+    <tableColumn id="26" xr3:uid="{6A29A013-FF84-400E-8F74-E5A850484E6D}" name="Abu Dhabi Grand Prix" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AA3744FF-5353-4C30-A94F-CE2FC15CD0CD}" name="Table6" displayName="Table6" ref="A1:AB48" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AA3744FF-5353-4C30-A94F-CE2FC15CD0CD}" name="Table6" displayName="Table6" ref="A1:AB48" totalsRowShown="0" headerRowDxfId="109" dataDxfId="108">
   <autoFilter ref="A1:AB48" xr:uid="{AA3744FF-5353-4C30-A94F-CE2FC15CD0CD}"/>
   <tableColumns count="28">
-    <tableColumn id="1" xr3:uid="{E278D08B-82F0-48D0-A658-DE818A33E0B8}" name="Driver" dataDxfId="29"/>
-    <tableColumn id="28" xr3:uid="{79CEAB9E-3A8C-4DF1-9F9B-E93533E41FBB}" name="Number" dataDxfId="28">
+    <tableColumn id="1" xr3:uid="{E278D08B-82F0-48D0-A658-DE818A33E0B8}" name="Driver" dataDxfId="3"/>
+    <tableColumn id="28" xr3:uid="{79CEAB9E-3A8C-4DF1-9F9B-E93533E41FBB}" name="Number" dataDxfId="4">
       <calculatedColumnFormula array="1">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00D7725B-DFFE-4C3A-ACCE-32C162A4E831}" name="Constructor" dataDxfId="27">
+    <tableColumn id="2" xr3:uid="{00D7725B-DFFE-4C3A-ACCE-32C162A4E831}" name="Constructor" dataDxfId="107">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8FDBF4AD-2961-4047-8F65-8E8ADEDC3502}" name="Team" dataDxfId="26">
+    <tableColumn id="3" xr3:uid="{8FDBF4AD-2961-4047-8F65-8E8ADEDC3502}" name="Team" dataDxfId="2">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{FEF76843-A12B-4494-995B-783FB04E6013}" name="Australian Grand Prix" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{17071EA5-F41C-4EBD-94F0-1B51429AF44F}" name="Chinese Grand Prix" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{F5001349-A1D5-43C9-97E1-9460CA742B63}" name="Japanese Grand Prix" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{6D0913D3-24E1-4ACA-B912-74174373B813}" name="Bahrain Grand Prix" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{E4C84672-BC98-4DF5-B9EE-8A8055F39F2D}" name="Saudi Arabian Grand Prix" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{BB7D339C-688A-4E60-8767-047C06319E68}" name="Miami Grand Prix" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{57075CE6-6548-4845-A50E-8AEFC61753A4}" name="Emilia Romagna Grand Prix" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{EE6736F8-ADB5-4E71-B05F-97594B3B3472}" name="Monaco Grand Prix" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{7968AD0F-F03C-43FE-9936-B9C133C05B68}" name="Spanish Grand Prix" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{B8990854-8E63-4954-BB66-C62E6A969529}" name="Canadian Grand Prix" dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{0E25BBA9-F83B-4D7F-B1E2-448AE6406574}" name="Austrian Grand Prix" dataDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{AFBF197F-D2AA-4D23-9095-09D50B18B3F7}" name="British Grand Prix" dataDxfId="14"/>
-    <tableColumn id="16" xr3:uid="{CF02CCED-BF33-4C52-A70B-20F8601C2B11}" name="Belgian Grand Prix" dataDxfId="13"/>
-    <tableColumn id="17" xr3:uid="{7104019E-E290-4E2A-85C1-75D032C22FCE}" name="Hungarian Grand Prix" dataDxfId="12"/>
-    <tableColumn id="18" xr3:uid="{FFF263A4-5EE2-49F0-9BA6-08425F3D3FE9}" name="Dutch Grand Prix" dataDxfId="11"/>
-    <tableColumn id="19" xr3:uid="{0A2EFD7F-EE8D-449A-ADD0-4CCC316EBCE8}" name="Italian Grand Prix" dataDxfId="10"/>
-    <tableColumn id="20" xr3:uid="{EB37AA19-112E-41AF-8572-4A071B7C2217}" name="Azerbaijan Grand Prix" dataDxfId="9"/>
-    <tableColumn id="21" xr3:uid="{E5F20E2D-66D0-473E-B944-BB69CCC67E52}" name="Singapore Grand Prix" dataDxfId="8"/>
-    <tableColumn id="22" xr3:uid="{2C2EEBC6-3F36-4C36-B283-0B40A3DEF047}" name="United States Grand Prix" dataDxfId="7"/>
-    <tableColumn id="23" xr3:uid="{F863F260-3241-4267-96F8-B19D16BA264E}" name="Mexico City Grand Prix" dataDxfId="6"/>
-    <tableColumn id="24" xr3:uid="{9076A145-7D0A-4875-BB6A-4FB7D295FC47}" name="São Paulo Grand Prix" dataDxfId="5"/>
-    <tableColumn id="25" xr3:uid="{E68C8DA5-1B26-4FD9-A9B3-04738D5CD8FB}" name="Las Vegas Grand Prix" dataDxfId="4"/>
-    <tableColumn id="26" xr3:uid="{149AD907-AF11-4CF7-A5B7-75B2C9170D15}" name="Qatar Grand Prix" dataDxfId="3"/>
-    <tableColumn id="27" xr3:uid="{940BCA92-8A19-4BC4-979F-FC730E0FF0D9}" name="Abu Dhabi Grand Prix" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{FEF76843-A12B-4494-995B-783FB04E6013}" name="Australian Grand Prix" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{17071EA5-F41C-4EBD-94F0-1B51429AF44F}" name="Chinese Grand Prix" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{F5001349-A1D5-43C9-97E1-9460CA742B63}" name="Japanese Grand Prix" dataDxfId="106"/>
+    <tableColumn id="7" xr3:uid="{6D0913D3-24E1-4ACA-B912-74174373B813}" name="Bahrain Grand Prix" dataDxfId="105"/>
+    <tableColumn id="8" xr3:uid="{E4C84672-BC98-4DF5-B9EE-8A8055F39F2D}" name="Saudi Arabian Grand Prix" dataDxfId="104"/>
+    <tableColumn id="9" xr3:uid="{BB7D339C-688A-4E60-8767-047C06319E68}" name="Miami Grand Prix" dataDxfId="103"/>
+    <tableColumn id="10" xr3:uid="{57075CE6-6548-4845-A50E-8AEFC61753A4}" name="Emilia Romagna Grand Prix" dataDxfId="102"/>
+    <tableColumn id="11" xr3:uid="{EE6736F8-ADB5-4E71-B05F-97594B3B3472}" name="Monaco Grand Prix" dataDxfId="101"/>
+    <tableColumn id="12" xr3:uid="{7968AD0F-F03C-43FE-9936-B9C133C05B68}" name="Spanish Grand Prix" dataDxfId="100"/>
+    <tableColumn id="13" xr3:uid="{B8990854-8E63-4954-BB66-C62E6A969529}" name="Canadian Grand Prix" dataDxfId="99"/>
+    <tableColumn id="14" xr3:uid="{0E25BBA9-F83B-4D7F-B1E2-448AE6406574}" name="Austrian Grand Prix" dataDxfId="98"/>
+    <tableColumn id="15" xr3:uid="{AFBF197F-D2AA-4D23-9095-09D50B18B3F7}" name="British Grand Prix" dataDxfId="97"/>
+    <tableColumn id="16" xr3:uid="{CF02CCED-BF33-4C52-A70B-20F8601C2B11}" name="Belgian Grand Prix" dataDxfId="96"/>
+    <tableColumn id="17" xr3:uid="{7104019E-E290-4E2A-85C1-75D032C22FCE}" name="Hungarian Grand Prix" dataDxfId="95"/>
+    <tableColumn id="18" xr3:uid="{FFF263A4-5EE2-49F0-9BA6-08425F3D3FE9}" name="Dutch Grand Prix" dataDxfId="94"/>
+    <tableColumn id="19" xr3:uid="{0A2EFD7F-EE8D-449A-ADD0-4CCC316EBCE8}" name="Italian Grand Prix" dataDxfId="93"/>
+    <tableColumn id="20" xr3:uid="{EB37AA19-112E-41AF-8572-4A071B7C2217}" name="Azerbaijan Grand Prix" dataDxfId="92"/>
+    <tableColumn id="21" xr3:uid="{E5F20E2D-66D0-473E-B944-BB69CCC67E52}" name="Singapore Grand Prix" dataDxfId="91"/>
+    <tableColumn id="22" xr3:uid="{2C2EEBC6-3F36-4C36-B283-0B40A3DEF047}" name="United States Grand Prix" dataDxfId="90"/>
+    <tableColumn id="23" xr3:uid="{F863F260-3241-4267-96F8-B19D16BA264E}" name="Mexico City Grand Prix" dataDxfId="89"/>
+    <tableColumn id="24" xr3:uid="{9076A145-7D0A-4875-BB6A-4FB7D295FC47}" name="São Paulo Grand Prix" dataDxfId="88"/>
+    <tableColumn id="25" xr3:uid="{E68C8DA5-1B26-4FD9-A9B3-04738D5CD8FB}" name="Las Vegas Grand Prix" dataDxfId="87"/>
+    <tableColumn id="26" xr3:uid="{149AD907-AF11-4CF7-A5B7-75B2C9170D15}" name="Qatar Grand Prix" dataDxfId="86"/>
+    <tableColumn id="27" xr3:uid="{940BCA92-8A19-4BC4-979F-FC730E0FF0D9}" name="Abu Dhabi Grand Prix" dataDxfId="85"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{84A8F2DB-5318-41DA-B2EB-50513DF6CCBA}" name="Table7" displayName="Table7" ref="A1:Z23" totalsRowShown="0" headerRowDxfId="65" dataDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{84A8F2DB-5318-41DA-B2EB-50513DF6CCBA}" name="Table7" displayName="Table7" ref="A1:Z23" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="A1:Z23" xr:uid="{84A8F2DB-5318-41DA-B2EB-50513DF6CCBA}"/>
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{04FE50CB-43CC-4C2C-B3E5-20381A77C6EE}" name="Driver" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{6F987E8C-773F-4CD7-8683-D3D2A2357DFC}" name="Constructor" dataDxfId="63">
+    <tableColumn id="1" xr3:uid="{04FE50CB-43CC-4C2C-B3E5-20381A77C6EE}" name="Driver" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{6F987E8C-773F-4CD7-8683-D3D2A2357DFC}" name="Constructor" dataDxfId="36">
       <calculatedColumnFormula>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F55A6B37-6EDE-41E4-B6B2-EE2FF245418C}" name="Australian Grand Prix" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{07D64B60-38BF-49D0-9F5A-DA0EB0A1CF21}" name="Chinese Grand Prix" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{1D828739-4FD5-40ED-A5B5-B23567BDE3FE}" name="Japanese Grand Prix" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{1062B4A0-6DF4-41F9-877D-4B43E48CCFE6}" name="Bahrain Grand Prix" dataDxfId="59"/>
-    <tableColumn id="7" xr3:uid="{1C734CE0-74E1-4F37-8C9E-9F2EE741BFE5}" name="Saudi Arabian Grand Prix" dataDxfId="58"/>
-    <tableColumn id="8" xr3:uid="{6DA07DD4-DD0E-4DB7-AEA7-F3A2E9225738}" name="Miami Grand Prix" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{257ED334-DEA1-4225-A408-3C2676795930}" name="Emilia Romagna Grand Prix" dataDxfId="56"/>
-    <tableColumn id="10" xr3:uid="{BAE89735-07AF-444C-B220-851C0CB3C754}" name="Monaco Grand Prix" dataDxfId="55"/>
-    <tableColumn id="11" xr3:uid="{B7D94A29-43B7-41DC-80C3-B1923F3E9284}" name="Spanish Grand Prix" dataDxfId="54"/>
-    <tableColumn id="12" xr3:uid="{21AA035A-318D-4FB7-BBBA-0C6D4F13E5CB}" name="Canadian Grand Prix" dataDxfId="53"/>
-    <tableColumn id="13" xr3:uid="{FACD5626-3EE1-4F7A-B7CB-6C80DE689297}" name="Austrian Grand Prix" dataDxfId="52"/>
-    <tableColumn id="14" xr3:uid="{D0953B36-F941-4B38-8251-D2477280E99D}" name="British Grand Prix" dataDxfId="51"/>
-    <tableColumn id="15" xr3:uid="{AC25F154-2768-4FDF-8473-44B8EF96F3F9}" name="Belgian Grand Prix" dataDxfId="50"/>
-    <tableColumn id="16" xr3:uid="{06BB5252-52C6-48F1-92DD-3677D94F6AD6}" name="Hungarian Grand Prix" dataDxfId="49"/>
-    <tableColumn id="17" xr3:uid="{6FCED645-DEDA-4065-8ED7-3401FF6E8A64}" name="Dutch Grand Prix" dataDxfId="48"/>
-    <tableColumn id="18" xr3:uid="{66976D97-649B-4E27-84FB-6BBBDE6B54DD}" name="Italian Grand Prix" dataDxfId="47"/>
-    <tableColumn id="19" xr3:uid="{41283C26-AE5C-4033-8465-C5C3B22E6094}" name="Azerbaijan Grand Prix" dataDxfId="46"/>
-    <tableColumn id="20" xr3:uid="{C4FE0C5A-0BCF-477D-ABC0-0A0D0583E97C}" name="Singapore Grand Prix" dataDxfId="45"/>
-    <tableColumn id="21" xr3:uid="{F69B7691-4E40-4AE7-846B-7BA48ADEE249}" name="United States Grand Prix" dataDxfId="44"/>
-    <tableColumn id="22" xr3:uid="{B7417A28-B404-40D9-AFF3-00A8B4A0C4D2}" name="Mexico City Grand Prix" dataDxfId="43"/>
-    <tableColumn id="23" xr3:uid="{FE4AA98D-B3DC-4364-BC04-FAE369D83855}" name="São Paulo Grand Prix" dataDxfId="42"/>
-    <tableColumn id="24" xr3:uid="{BCBF9F5E-E462-49BA-87E9-6620D01608A4}" name="Las Vegas Grand Prix" dataDxfId="41"/>
-    <tableColumn id="25" xr3:uid="{5963F622-6118-42F5-BD17-0A2B097489EC}" name="Qatar Grand Prix" dataDxfId="40"/>
-    <tableColumn id="26" xr3:uid="{2B6C136A-A691-419C-9E4E-23006C9A0B32}" name="Abu Dhabi Grand Prix" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{F55A6B37-6EDE-41E4-B6B2-EE2FF245418C}" name="Australian Grand Prix" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{07D64B60-38BF-49D0-9F5A-DA0EB0A1CF21}" name="Chinese Grand Prix" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{1D828739-4FD5-40ED-A5B5-B23567BDE3FE}" name="Japanese Grand Prix" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{1062B4A0-6DF4-41F9-877D-4B43E48CCFE6}" name="Bahrain Grand Prix" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{1C734CE0-74E1-4F37-8C9E-9F2EE741BFE5}" name="Saudi Arabian Grand Prix" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{6DA07DD4-DD0E-4DB7-AEA7-F3A2E9225738}" name="Miami Grand Prix" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{257ED334-DEA1-4225-A408-3C2676795930}" name="Emilia Romagna Grand Prix" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{BAE89735-07AF-444C-B220-851C0CB3C754}" name="Monaco Grand Prix" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{B7D94A29-43B7-41DC-80C3-B1923F3E9284}" name="Spanish Grand Prix" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{21AA035A-318D-4FB7-BBBA-0C6D4F13E5CB}" name="Canadian Grand Prix" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{FACD5626-3EE1-4F7A-B7CB-6C80DE689297}" name="Austrian Grand Prix" dataDxfId="25"/>
+    <tableColumn id="14" xr3:uid="{D0953B36-F941-4B38-8251-D2477280E99D}" name="British Grand Prix" dataDxfId="24"/>
+    <tableColumn id="15" xr3:uid="{AC25F154-2768-4FDF-8473-44B8EF96F3F9}" name="Belgian Grand Prix" dataDxfId="23"/>
+    <tableColumn id="16" xr3:uid="{06BB5252-52C6-48F1-92DD-3677D94F6AD6}" name="Hungarian Grand Prix" dataDxfId="22"/>
+    <tableColumn id="17" xr3:uid="{6FCED645-DEDA-4065-8ED7-3401FF6E8A64}" name="Dutch Grand Prix" dataDxfId="21"/>
+    <tableColumn id="18" xr3:uid="{66976D97-649B-4E27-84FB-6BBBDE6B54DD}" name="Italian Grand Prix" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{41283C26-AE5C-4033-8465-C5C3B22E6094}" name="Azerbaijan Grand Prix" dataDxfId="19"/>
+    <tableColumn id="20" xr3:uid="{C4FE0C5A-0BCF-477D-ABC0-0A0D0583E97C}" name="Singapore Grand Prix" dataDxfId="18"/>
+    <tableColumn id="21" xr3:uid="{F69B7691-4E40-4AE7-846B-7BA48ADEE249}" name="United States Grand Prix" dataDxfId="17"/>
+    <tableColumn id="22" xr3:uid="{B7417A28-B404-40D9-AFF3-00A8B4A0C4D2}" name="Mexico City Grand Prix" dataDxfId="16"/>
+    <tableColumn id="23" xr3:uid="{FE4AA98D-B3DC-4364-BC04-FAE369D83855}" name="São Paulo Grand Prix" dataDxfId="15"/>
+    <tableColumn id="24" xr3:uid="{BCBF9F5E-E462-49BA-87E9-6620D01608A4}" name="Las Vegas Grand Prix" dataDxfId="14"/>
+    <tableColumn id="25" xr3:uid="{5963F622-6118-42F5-BD17-0A2B097489EC}" name="Qatar Grand Prix" dataDxfId="13"/>
+    <tableColumn id="26" xr3:uid="{2B6C136A-A691-419C-9E4E-23006C9A0B32}" name="Abu Dhabi Grand Prix" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{50C8425B-C655-4E04-A073-CF7E04AF601A}" name="Table5" displayName="Table5" ref="A1:E23" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{50C8425B-C655-4E04-A073-CF7E04AF601A}" name="Table5" displayName="Table5" ref="A1:E23" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:E23" xr:uid="{50C8425B-C655-4E04-A073-CF7E04AF601A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D9288ECF-7FB6-413D-B1F9-D0C1F542379A}" name="Team Name" dataDxfId="36">
+    <tableColumn id="1" xr3:uid="{D9288ECF-7FB6-413D-B1F9-D0C1F542379A}" name="Team Name" dataDxfId="9">
       <calculatedColumnFormula>_xlfn.XLOOKUP(C2,Drivers!$B$2:$B$23,Drivers!$C$2:$C$23,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9F22078D-54A1-4A4A-AF23-B4137F60AB3E}" name="Constructor" dataDxfId="35">
+    <tableColumn id="2" xr3:uid="{9F22078D-54A1-4A4A-AF23-B4137F60AB3E}" name="Constructor" dataDxfId="8">
       <calculatedColumnFormula>_xlfn.XLOOKUP(C2,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8E3FB958-7BB0-400F-A3F5-E8EC1EDBE678}" name="Driver" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{386A61E9-CDA2-4647-81AE-9E7EE26F203F}" name="Engine/Power Unit" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{FECB8E79-446F-4614-9058-29E64F3CE65C}" name="Chassis" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{8E3FB958-7BB0-400F-A3F5-E8EC1EDBE678}" name="Driver" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{386A61E9-CDA2-4647-81AE-9E7EE26F203F}" name="Engine/Power Unit" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{FECB8E79-446F-4614-9058-29E64F3CE65C}" name="Chassis" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4594,376 +4651,376 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="19">
         <v>10</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="19" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="3" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="19">
         <v>43</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="19" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="4" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="19">
         <v>14</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="19" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="5" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="19">
         <v>18</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="19" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <v>23</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="19" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="7" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="19">
         <v>55</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="19" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="19">
         <v>5</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="19" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="9" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="19">
         <v>27</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="19" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="10" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="19">
         <v>11</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="19" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="11" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <v>77</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="19" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="12" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="19">
         <v>16</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="19">
         <v>44</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="19">
         <v>31</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="19" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="19">
         <v>87</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="19" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="2:26" x14ac:dyDescent="0.3">
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="19">
         <v>1</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="19">
         <v>81</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="19" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="19">
         <v>12</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="19" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="19">
         <v>63</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="19" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="19">
         <v>30</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="19" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="19">
         <v>41</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="19" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="19">
         <v>3</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="19" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="19">
         <v>6</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="19" t="s">
         <v>129</v>
       </c>
     </row>
@@ -5011,7 +5068,7 @@
     <col min="5" max="5" width="13" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.33203125" style="3" customWidth="1"/>
     <col min="7" max="7" width="13.77734375" style="3" customWidth="1"/>
-    <col min="8" max="10" width="18.5546875" style="19" customWidth="1"/>
+    <col min="8" max="10" width="18.5546875" style="18" customWidth="1"/>
     <col min="11" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
@@ -5034,13 +5091,13 @@
       <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="17" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5054,7 +5111,7 @@
       <c r="D3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="22">
         <v>46089</v>
       </c>
       <c r="F3" s="3">
@@ -5384,210 +5441,210 @@
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="I32" s="21"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="I32" s="20"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="I33" s="21"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="I33" s="20"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="I34" s="21"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="I34" s="20"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="I35" s="21"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="I35" s="20"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="I36" s="21"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="I36" s="20"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="I37" s="21"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="I37" s="20"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="I38" s="21"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="I38" s="20"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="I39" s="21"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="I39" s="20"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="I40" s="21"/>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="I40" s="20"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="I41" s="21"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="I41" s="20"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="I42" s="21"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="I42" s="20"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="I43" s="21"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="I43" s="20"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="I44" s="21"/>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="I44" s="20"/>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B45" s="20"/>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="I45" s="21"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="I45" s="20"/>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B46" s="20"/>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="I46" s="21"/>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="I46" s="20"/>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B47" s="20"/>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="I47" s="21"/>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="I47" s="20"/>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B48" s="20"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="I48" s="21"/>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="I48" s="20"/>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="I49" s="21"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="I49" s="20"/>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B50" s="20"/>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="20"/>
-      <c r="I50" s="21"/>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="I50" s="20"/>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B51" s="20"/>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="I51" s="21"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="I51" s="20"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" s="20"/>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="I52" s="21"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="I52" s="20"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53" s="20"/>
-      <c r="C53" s="20"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="I53" s="21"/>
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="I53" s="20"/>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B54" s="20"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="I54" s="21"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="I54" s="20"/>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B55" s="20"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
-      <c r="I55" s="21"/>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="I55" s="20"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B56" s="20"/>
-      <c r="C56" s="20"/>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B57" s="20" t="s">
+      <c r="B57" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6025,110 +6082,176 @@
       <c r="A27" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="B27" s="9">
+        <v>5</v>
+      </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="B28" s="9">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="B29" s="9">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="B30" s="9">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>115</v>
       </c>
+      <c r="B31" s="9">
+        <v>15</v>
+      </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B32" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B33" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B34" s="9">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B35" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B36" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B37" s="9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B38" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B39" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B40" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B41" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B42" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B43" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B44" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B45" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B46" s="9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B47" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>121</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -6144,20 +6267,21 @@
   <dimension ref="A1:AC48"/>
   <sheetFormatPr defaultRowHeight="13.8" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" style="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="26" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.6640625" style="14" customWidth="1" outlineLevel="1"/>
     <col min="4" max="4" width="41.88671875" style="14" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="28" width="8.5546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="6" max="28" width="8.5546875" style="15" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7" style="15" bestFit="1" customWidth="1"/>
     <col min="30" max="16384" width="8.88671875" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="13" customFormat="1" ht="130.80000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:29" s="13" customFormat="1" ht="129.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="24" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="8" t="s">
@@ -6240,11 +6364,11 @@
       </c>
     </row>
     <row r="2" spans="1:29" s="13" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
-      <c r="B2" s="25"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="24"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="29" t="s">
         <v>122</v>
       </c>
       <c r="F2" s="12" t="s">
@@ -6318,1045 +6442,1115 @@
       </c>
     </row>
     <row r="3" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="26" cm="1">
+      <c r="B3" s="25" cm="1">
         <f t="array" ref="B3">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>10</v>
       </c>
-      <c r="C3" s="24" t="str">
+      <c r="C3" s="23" t="str">
         <f>_xlfn.XLOOKUP(A3,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Alpine-Mercedes</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="23" t="str">
         <f>_xlfn.XLOOKUP(A3,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>France BWT Alpine F1 Team</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="27">
         <v>3.7679999999999998</v>
       </c>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
     </row>
     <row r="4" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="26" cm="1">
+      <c r="B4" s="25" cm="1">
         <f t="array" ref="B4">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>43</v>
       </c>
-      <c r="C4" s="24" t="str">
+      <c r="C4" s="23" t="str">
         <f>_xlfn.XLOOKUP(A4,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Alpine-Mercedes</v>
       </c>
-      <c r="D4" s="24" t="str">
+      <c r="D4" s="23" t="str">
         <f>_xlfn.XLOOKUP(A4,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>France BWT Alpine F1 Team</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="27">
         <v>3.0579999999999998</v>
       </c>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
     </row>
     <row r="5" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="26" cm="1">
+      <c r="B5" s="25" cm="1">
         <f t="array" ref="B5">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>14</v>
       </c>
-      <c r="C5" s="24" t="str">
+      <c r="C5" s="23" t="str">
         <f>_xlfn.XLOOKUP(A5,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Aston Martin Aramco-Honda</v>
       </c>
-      <c r="D5" s="24" t="str">
+      <c r="D5" s="23" t="str">
         <f>_xlfn.XLOOKUP(A5,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United Kingdom Aston Martin Aramco F1 Team</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="27">
         <v>0</v>
       </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="22"/>
-      <c r="L5" s="22"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
     </row>
     <row r="6" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="26" cm="1">
+      <c r="B6" s="25" cm="1">
         <f t="array" ref="B6">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>18</v>
       </c>
-      <c r="C6" s="24" t="str">
+      <c r="C6" s="23" t="str">
         <f>_xlfn.XLOOKUP(A6,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Aston Martin Aramco-Honda</v>
       </c>
-      <c r="D6" s="24" t="str">
+      <c r="D6" s="23" t="str">
         <f>_xlfn.XLOOKUP(A6,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United Kingdom Aston Martin Aramco F1 Team</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="27">
         <v>30.067</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
     </row>
     <row r="7" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="26" cm="1">
+      <c r="B7" s="25" cm="1">
         <f t="array" ref="B7">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>23</v>
       </c>
-      <c r="C7" s="24" t="str">
+      <c r="C7" s="23" t="str">
         <f>_xlfn.XLOOKUP(A7,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Atlassian Williams-Mercedes</v>
       </c>
-      <c r="D7" s="24" t="str">
+      <c r="D7" s="23" t="str">
         <f>_xlfn.XLOOKUP(A7,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United Kingdom Atlassian Williams F1 Team</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="27">
         <v>2.863</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
     </row>
     <row r="8" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="26" cm="1">
+      <c r="B8" s="25" cm="1">
         <f t="array" ref="B8">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>55</v>
       </c>
-      <c r="C8" s="24" t="str">
+      <c r="C8" s="23" t="str">
         <f>_xlfn.XLOOKUP(A8,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Atlassian Williams-Mercedes</v>
       </c>
-      <c r="D8" s="24" t="str">
+      <c r="D8" s="23" t="str">
         <f>_xlfn.XLOOKUP(A8,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United Kingdom Atlassian Williams F1 Team</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="27">
         <v>2.056</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
     </row>
     <row r="9" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="26" cm="1">
+      <c r="B9" s="25" cm="1">
         <f t="array" ref="B9">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>5</v>
       </c>
-      <c r="C9" s="24" t="str">
+      <c r="C9" s="23" t="str">
         <f>_xlfn.XLOOKUP(A9,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Audi</v>
       </c>
-      <c r="D9" s="24" t="str">
+      <c r="D9" s="23" t="str">
         <f>_xlfn.XLOOKUP(A9,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Germany Audi Revolut F1 Team</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="27">
         <v>1.429</v>
       </c>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
     </row>
     <row r="10" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="26" cm="1">
+      <c r="B10" s="25" cm="1">
         <f t="array" ref="B10">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>27</v>
       </c>
-      <c r="C10" s="24" t="str">
+      <c r="C10" s="23" t="str">
         <f>_xlfn.XLOOKUP(A10,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Audi</v>
       </c>
-      <c r="D10" s="24" t="str">
+      <c r="D10" s="23" t="str">
         <f>_xlfn.XLOOKUP(A10,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Germany Audi Revolut F1 Team</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="27">
         <v>1.702</v>
       </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
     </row>
     <row r="11" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="26" cm="1">
+      <c r="B11" s="25" cm="1">
         <f t="array" ref="B11">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>11</v>
       </c>
-      <c r="C11" s="24" t="str">
+      <c r="C11" s="23" t="str">
         <f>_xlfn.XLOOKUP(A11,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Cadillac-Ferrari</v>
       </c>
-      <c r="D11" s="24" t="str">
+      <c r="D11" s="23" t="str">
         <f>_xlfn.XLOOKUP(A11,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United States Cadillac Formula 1 Team</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="27">
         <v>4.3529999999999998</v>
       </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
     </row>
     <row r="12" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="B12" s="26" cm="1">
+      <c r="B12" s="25" cm="1">
         <f t="array" ref="B12">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>77</v>
       </c>
-      <c r="C12" s="24" t="str">
+      <c r="C12" s="23" t="str">
         <f>_xlfn.XLOOKUP(A12,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Cadillac-Ferrari</v>
       </c>
-      <c r="D12" s="24" t="str">
+      <c r="D12" s="23" t="str">
         <f>_xlfn.XLOOKUP(A12,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United States Cadillac Formula 1 Team</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="27">
         <v>3.7549999999999999</v>
       </c>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
     </row>
     <row r="13" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="26" cm="1">
+      <c r="B13" s="25" cm="1">
         <f t="array" ref="B13">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>16</v>
       </c>
-      <c r="C13" s="24" t="str">
+      <c r="C13" s="23" t="str">
         <f>_xlfn.XLOOKUP(A13,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Ferrari</v>
       </c>
-      <c r="D13" s="24" t="str">
+      <c r="D13" s="23" t="str">
         <f>_xlfn.XLOOKUP(A13,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Italy Scuderia Ferrari HP</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="21">
         <v>9.2901620370370371E-4</v>
       </c>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="AC13" s="29">
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="AC13" s="28">
         <f>Table6[[#This Row],[Australian Grand Prix]]+E14</f>
         <v>0.4699290162037037</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="26" cm="1">
+      <c r="B14" s="25" cm="1">
         <f t="array" ref="B14">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>44</v>
       </c>
-      <c r="C14" s="24" t="str">
+      <c r="C14" s="23" t="str">
         <f>_xlfn.XLOOKUP(A14,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Ferrari</v>
       </c>
-      <c r="D14" s="24" t="str">
+      <c r="D14" s="23" t="str">
         <f>_xlfn.XLOOKUP(A14,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Italy Scuderia Ferrari HP</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="27">
         <v>0.46899999999999997</v>
       </c>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
     </row>
     <row r="15" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="26" cm="1">
+      <c r="B15" s="25" cm="1">
         <f t="array" ref="B15">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>31</v>
       </c>
-      <c r="C15" s="24" t="str">
+      <c r="C15" s="23" t="str">
         <f>_xlfn.XLOOKUP(A15,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Haas-Ferrari</v>
       </c>
-      <c r="D15" s="24" t="str">
+      <c r="D15" s="23" t="str">
         <f>_xlfn.XLOOKUP(A15,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United States TGR Haas F1 Team</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="27">
         <v>1.8939999999999999</v>
       </c>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
     </row>
     <row r="16" spans="1:29" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="26" cm="1">
+      <c r="B16" s="25" cm="1">
         <f t="array" ref="B16">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>87</v>
       </c>
-      <c r="C16" s="24" t="str">
+      <c r="C16" s="23" t="str">
         <f>_xlfn.XLOOKUP(A16,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Haas-Ferrari</v>
       </c>
-      <c r="D16" s="24" t="str">
+      <c r="D16" s="23" t="str">
         <f>_xlfn.XLOOKUP(A16,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United States TGR Haas F1 Team</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="27">
         <v>2.415</v>
       </c>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
     </row>
     <row r="17" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="26" cm="1">
+      <c r="B17" s="25" cm="1">
         <f t="array" ref="B17">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>1</v>
       </c>
-      <c r="C17" s="24" t="str">
+      <c r="C17" s="23" t="str">
         <f>_xlfn.XLOOKUP(A17,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>McLaren-Mercedes</v>
       </c>
-      <c r="D17" s="24" t="str">
+      <c r="D17" s="23" t="str">
         <f>_xlfn.XLOOKUP(A17,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United Kingdom McLaren Mastercard F1 Team</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="27">
         <v>4.1239999999999997</v>
       </c>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="21"/>
     </row>
     <row r="18" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="26" cm="1">
+      <c r="B18" s="25" cm="1">
         <f t="array" ref="B18">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>81</v>
       </c>
-      <c r="C18" s="24" t="str">
+      <c r="C18" s="23" t="str">
         <f>_xlfn.XLOOKUP(A18,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>McLaren-Mercedes</v>
       </c>
-      <c r="D18" s="24" t="str">
+      <c r="D18" s="23" t="str">
         <f>_xlfn.XLOOKUP(A18,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United Kingdom McLaren Mastercard F1 Team</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="27">
         <v>1.075</v>
       </c>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="21"/>
     </row>
     <row r="19" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="B19" s="26" cm="1">
+      <c r="B19" s="25" cm="1">
         <f t="array" ref="B19">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>12</v>
       </c>
-      <c r="C19" s="24" t="str">
+      <c r="C19" s="23" t="str">
         <f>_xlfn.XLOOKUP(A19,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Mercedes</v>
       </c>
-      <c r="D19" s="24" t="str">
+      <c r="D19" s="23" t="str">
         <f>_xlfn.XLOOKUP(A19,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Germany Mercedes-AMG Petronas F1 Team</v>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="27">
         <v>1.109</v>
       </c>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
     </row>
     <row r="20" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="26" cm="1">
+      <c r="B20" s="25" cm="1">
         <f t="array" ref="B20">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>63</v>
       </c>
-      <c r="C20" s="24" t="str">
+      <c r="C20" s="23" t="str">
         <f>_xlfn.XLOOKUP(A20,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Mercedes</v>
       </c>
-      <c r="D20" s="24" t="str">
+      <c r="D20" s="23" t="str">
         <f>_xlfn.XLOOKUP(A20,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Germany Mercedes-AMG Petronas F1 Team</v>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="27">
         <v>1.1040000000000001</v>
       </c>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
     </row>
     <row r="21" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="26" cm="1">
+      <c r="B21" s="25" cm="1">
         <f t="array" ref="B21">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>30</v>
       </c>
-      <c r="C21" s="24" t="str">
+      <c r="C21" s="23" t="str">
         <f>_xlfn.XLOOKUP(A21,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Racing Bulls-Red Bull Ford</v>
       </c>
-      <c r="D21" s="24" t="str">
+      <c r="D21" s="23" t="str">
         <f>_xlfn.XLOOKUP(A21,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Italy Visa Cash App Racing Bulls F1 Team</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="27">
         <v>2.3460000000000001</v>
       </c>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
     </row>
     <row r="22" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="B22" s="26" cm="1">
+      <c r="B22" s="25" cm="1">
         <f t="array" ref="B22">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>41</v>
       </c>
-      <c r="C22" s="24" t="str">
+      <c r="C22" s="23" t="str">
         <f>_xlfn.XLOOKUP(A22,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Racing Bulls-Red Bull Ford</v>
       </c>
-      <c r="D22" s="24" t="str">
+      <c r="D22" s="23" t="str">
         <f>_xlfn.XLOOKUP(A22,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Italy Visa Cash App Racing Bulls F1 Team</v>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="27">
         <v>1.046</v>
       </c>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="21"/>
     </row>
     <row r="23" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="26" cm="1">
+      <c r="B23" s="25" cm="1">
         <f t="array" ref="B23">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>3</v>
       </c>
-      <c r="C23" s="24" t="str">
+      <c r="C23" s="23" t="str">
         <f>_xlfn.XLOOKUP(A23,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Red Bull Racing-Red Bull Ford</v>
       </c>
-      <c r="D23" s="24" t="str">
+      <c r="D23" s="23" t="str">
         <f>_xlfn.XLOOKUP(A23,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Austria Oracle Red Bull Racing</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="27">
         <v>0.52200000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="26" cm="1">
+      <c r="B24" s="25" cm="1">
         <f t="array" ref="B24">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>6</v>
       </c>
-      <c r="C24" s="24" t="str">
+      <c r="C24" s="23" t="str">
         <f>_xlfn.XLOOKUP(A24,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Red Bull Racing-Red Bull Ford</v>
       </c>
-      <c r="D24" s="24" t="str">
+      <c r="D24" s="23" t="str">
         <f>_xlfn.XLOOKUP(A24,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Austria Oracle Red Bull Racing</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="27">
         <v>0.82</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="C25" s="24" t="str">
+      <c r="C25" s="23" t="str">
         <f>_xlfn.XLOOKUP(A25,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v/>
       </c>
-      <c r="D25" s="24" t="str">
+      <c r="D25" s="23" t="str">
         <f>_xlfn.XLOOKUP(A25,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="E26" s="16" t="s">
+    <row r="26" spans="1:28" s="31" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="35"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="I26" s="16" t="s">
+      <c r="I26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="J26" s="16" t="s">
+      <c r="J26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="K26" s="16" t="s">
+      <c r="K26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="L26" s="16" t="s">
+      <c r="L26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="M26" s="16" t="s">
+      <c r="M26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="N26" s="16" t="s">
+      <c r="N26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="O26" s="16" t="s">
+      <c r="O26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="P26" s="16" t="s">
+      <c r="P26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="Q26" s="16" t="s">
+      <c r="Q26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="R26" s="16" t="s">
+      <c r="R26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="S26" s="16" t="s">
+      <c r="S26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T26" s="16" t="s">
+      <c r="T26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="U26" s="16" t="s">
+      <c r="U26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="V26" s="16" t="s">
+      <c r="V26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="W26" s="16" t="s">
+      <c r="W26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="X26" s="16" t="s">
+      <c r="X26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="Y26" s="16" t="s">
+      <c r="Y26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="Z26" s="16" t="s">
+      <c r="Z26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="AA26" s="16" t="s">
+      <c r="AA26" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="AB26" s="16" t="s">
+      <c r="AB26" s="30" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="B27" s="26" cm="1">
+      <c r="B27" s="25" cm="1">
         <f t="array" ref="B27">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>10</v>
       </c>
-      <c r="C27" s="24" t="str">
+      <c r="C27" s="23" t="str">
         <f>_xlfn.XLOOKUP(A27,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Alpine-Mercedes</v>
       </c>
-      <c r="D27" s="24" t="str">
+      <c r="D27" s="23" t="str">
         <f>_xlfn.XLOOKUP(A27,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>France BWT Alpine F1 Team</v>
       </c>
+      <c r="E27" s="26" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="28" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="B28" s="26" cm="1">
+      <c r="B28" s="25" cm="1">
         <f t="array" ref="B28">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>43</v>
       </c>
-      <c r="C28" s="24" t="str">
+      <c r="C28" s="23" t="str">
         <f>_xlfn.XLOOKUP(A28,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Alpine-Mercedes</v>
       </c>
-      <c r="D28" s="24" t="str">
+      <c r="D28" s="23" t="str">
         <f>_xlfn.XLOOKUP(A28,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>France BWT Alpine F1 Team</v>
       </c>
+      <c r="E28" s="26" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="29" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="26" cm="1">
+      <c r="B29" s="25" cm="1">
         <f t="array" ref="B29">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>14</v>
       </c>
-      <c r="C29" s="24" t="str">
+      <c r="C29" s="23" t="str">
         <f>_xlfn.XLOOKUP(A29,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Aston Martin Aramco-Honda</v>
       </c>
-      <c r="D29" s="24" t="str">
+      <c r="D29" s="23" t="str">
         <f>_xlfn.XLOOKUP(A29,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United Kingdom Aston Martin Aramco F1 Team</v>
       </c>
+      <c r="E29" s="26" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="30" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="26" cm="1">
+      <c r="B30" s="25" cm="1">
         <f t="array" ref="B30">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>18</v>
       </c>
-      <c r="C30" s="24" t="str">
+      <c r="C30" s="23" t="str">
         <f>_xlfn.XLOOKUP(A30,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Aston Martin Aramco-Honda</v>
       </c>
-      <c r="D30" s="24" t="str">
+      <c r="D30" s="23" t="str">
         <f>_xlfn.XLOOKUP(A30,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United Kingdom Aston Martin Aramco F1 Team</v>
       </c>
+      <c r="E30" s="26" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="31" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="26" cm="1">
+      <c r="B31" s="25" cm="1">
         <f t="array" ref="B31">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>23</v>
       </c>
-      <c r="C31" s="24" t="str">
+      <c r="C31" s="23" t="str">
         <f>_xlfn.XLOOKUP(A31,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Atlassian Williams-Mercedes</v>
       </c>
-      <c r="D31" s="24" t="str">
+      <c r="D31" s="23" t="str">
         <f>_xlfn.XLOOKUP(A31,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United Kingdom Atlassian Williams F1 Team</v>
       </c>
+      <c r="E31" s="26" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="32" spans="1:28" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="26" cm="1">
+      <c r="B32" s="25" cm="1">
         <f t="array" ref="B32">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>55</v>
       </c>
-      <c r="C32" s="24" t="str">
+      <c r="C32" s="23" t="str">
         <f>_xlfn.XLOOKUP(A32,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Atlassian Williams-Mercedes</v>
       </c>
-      <c r="D32" s="24" t="str">
+      <c r="D32" s="23" t="str">
         <f>_xlfn.XLOOKUP(A32,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United Kingdom Atlassian Williams F1 Team</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="s">
+      <c r="E32" s="26" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B33" s="26" cm="1">
+      <c r="B33" s="25" cm="1">
         <f t="array" ref="B33">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>5</v>
       </c>
-      <c r="C33" s="24" t="str">
+      <c r="C33" s="23" t="str">
         <f>_xlfn.XLOOKUP(A33,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Audi</v>
       </c>
-      <c r="D33" s="24" t="str">
+      <c r="D33" s="23" t="str">
         <f>_xlfn.XLOOKUP(A33,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Germany Audi Revolut F1 Team</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="20" t="s">
+      <c r="E33" s="26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="26" cm="1">
+      <c r="B34" s="25" cm="1">
         <f t="array" ref="B34">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>27</v>
       </c>
-      <c r="C34" s="24" t="str">
+      <c r="C34" s="23" t="str">
         <f>_xlfn.XLOOKUP(A34,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Audi</v>
       </c>
-      <c r="D34" s="24" t="str">
+      <c r="D34" s="23" t="str">
         <f>_xlfn.XLOOKUP(A34,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Germany Audi Revolut F1 Team</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="s">
+      <c r="E34" s="26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="26" cm="1">
+      <c r="B35" s="25" cm="1">
         <f t="array" ref="B35">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>11</v>
       </c>
-      <c r="C35" s="24" t="str">
+      <c r="C35" s="23" t="str">
         <f>_xlfn.XLOOKUP(A35,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Cadillac-Ferrari</v>
       </c>
-      <c r="D35" s="24" t="str">
+      <c r="D35" s="23" t="str">
         <f>_xlfn.XLOOKUP(A35,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United States Cadillac Formula 1 Team</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="20" t="s">
+      <c r="E35" s="26" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="B36" s="26" cm="1">
+      <c r="B36" s="25" cm="1">
         <f t="array" ref="B36">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>77</v>
       </c>
-      <c r="C36" s="24" t="str">
+      <c r="C36" s="23" t="str">
         <f>_xlfn.XLOOKUP(A36,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Cadillac-Ferrari</v>
       </c>
-      <c r="D36" s="24" t="str">
+      <c r="D36" s="23" t="str">
         <f>_xlfn.XLOOKUP(A36,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United States Cadillac Formula 1 Team</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="20" t="s">
+      <c r="E36" s="26" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="26" cm="1">
+      <c r="B37" s="25" cm="1">
         <f t="array" ref="B37">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>16</v>
       </c>
-      <c r="C37" s="24" t="str">
+      <c r="C37" s="23" t="str">
         <f>_xlfn.XLOOKUP(A37,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Ferrari</v>
       </c>
-      <c r="D37" s="24" t="str">
+      <c r="D37" s="23" t="str">
         <f>_xlfn.XLOOKUP(A37,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Italy Scuderia Ferrari HP</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="20" t="s">
+      <c r="E37" s="26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="26" cm="1">
+      <c r="B38" s="25" cm="1">
         <f t="array" ref="B38">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>44</v>
       </c>
-      <c r="C38" s="24" t="str">
+      <c r="C38" s="23" t="str">
         <f>_xlfn.XLOOKUP(A38,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Ferrari</v>
       </c>
-      <c r="D38" s="24" t="str">
+      <c r="D38" s="23" t="str">
         <f>_xlfn.XLOOKUP(A38,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Italy Scuderia Ferrari HP</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A39" s="20" t="s">
+      <c r="E38" s="26" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="26" cm="1">
+      <c r="B39" s="25" cm="1">
         <f t="array" ref="B39">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>31</v>
       </c>
-      <c r="C39" s="24" t="str">
+      <c r="C39" s="23" t="str">
         <f>_xlfn.XLOOKUP(A39,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Haas-Ferrari</v>
       </c>
-      <c r="D39" s="24" t="str">
+      <c r="D39" s="23" t="str">
         <f>_xlfn.XLOOKUP(A39,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United States TGR Haas F1 Team</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A40" s="20" t="s">
+      <c r="E39" s="26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="26" cm="1">
+      <c r="B40" s="25" cm="1">
         <f t="array" ref="B40">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>87</v>
       </c>
-      <c r="C40" s="24" t="str">
+      <c r="C40" s="23" t="str">
         <f>_xlfn.XLOOKUP(A40,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Haas-Ferrari</v>
       </c>
-      <c r="D40" s="24" t="str">
+      <c r="D40" s="23" t="str">
         <f>_xlfn.XLOOKUP(A40,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United States TGR Haas F1 Team</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="20" t="s">
+      <c r="E40" s="26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B41" s="26" cm="1">
+      <c r="B41" s="25" cm="1">
         <f t="array" ref="B41">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>1</v>
       </c>
-      <c r="C41" s="24" t="str">
+      <c r="C41" s="23" t="str">
         <f>_xlfn.XLOOKUP(A41,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>McLaren-Mercedes</v>
       </c>
-      <c r="D41" s="24" t="str">
+      <c r="D41" s="23" t="str">
         <f>_xlfn.XLOOKUP(A41,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United Kingdom McLaren Mastercard F1 Team</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="20" t="s">
+      <c r="E41" s="26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B42" s="26" cm="1">
+      <c r="B42" s="25" cm="1">
         <f t="array" ref="B42">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>81</v>
       </c>
-      <c r="C42" s="24" t="str">
+      <c r="C42" s="23" t="str">
         <f>_xlfn.XLOOKUP(A42,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>McLaren-Mercedes</v>
       </c>
-      <c r="D42" s="24" t="str">
+      <c r="D42" s="23" t="str">
         <f>_xlfn.XLOOKUP(A42,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>United Kingdom McLaren Mastercard F1 Team</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="20" t="s">
+      <c r="E42" s="26" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="B43" s="26" cm="1">
+      <c r="B43" s="25" cm="1">
         <f t="array" ref="B43">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>12</v>
       </c>
-      <c r="C43" s="24" t="str">
+      <c r="C43" s="23" t="str">
         <f>_xlfn.XLOOKUP(A43,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Mercedes</v>
       </c>
-      <c r="D43" s="24" t="str">
+      <c r="D43" s="23" t="str">
         <f>_xlfn.XLOOKUP(A43,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Germany Mercedes-AMG Petronas F1 Team</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A44" s="20" t="s">
+      <c r="E43" s="26" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="26" cm="1">
+      <c r="B44" s="25" cm="1">
         <f t="array" ref="B44">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>63</v>
       </c>
-      <c r="C44" s="24" t="str">
+      <c r="C44" s="23" t="str">
         <f>_xlfn.XLOOKUP(A44,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Mercedes</v>
       </c>
-      <c r="D44" s="24" t="str">
+      <c r="D44" s="23" t="str">
         <f>_xlfn.XLOOKUP(A44,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Germany Mercedes-AMG Petronas F1 Team</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A45" s="20" t="s">
+      <c r="E44" s="26">
+        <v>5.7717604166666672E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="26" cm="1">
+      <c r="B45" s="25" cm="1">
         <f t="array" ref="B45">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>30</v>
       </c>
-      <c r="C45" s="24" t="str">
+      <c r="C45" s="23" t="str">
         <f>_xlfn.XLOOKUP(A45,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Racing Bulls-Red Bull Ford</v>
       </c>
-      <c r="D45" s="24" t="str">
+      <c r="D45" s="23" t="str">
         <f>_xlfn.XLOOKUP(A45,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Italy Visa Cash App Racing Bulls F1 Team</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="20" t="s">
+      <c r="E45" s="26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="B46" s="26" cm="1">
+      <c r="B46" s="25" cm="1">
         <f t="array" ref="B46">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>41</v>
       </c>
-      <c r="C46" s="24" t="str">
+      <c r="C46" s="23" t="str">
         <f>_xlfn.XLOOKUP(A46,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Racing Bulls-Red Bull Ford</v>
       </c>
-      <c r="D46" s="24" t="str">
+      <c r="D46" s="23" t="str">
         <f>_xlfn.XLOOKUP(A46,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Italy Visa Cash App Racing Bulls F1 Team</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A47" s="20" t="s">
+      <c r="E46" s="26" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A47" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="26" cm="1">
+      <c r="B47" s="25" cm="1">
         <f t="array" ref="B47">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>3</v>
       </c>
-      <c r="C47" s="24" t="str">
+      <c r="C47" s="23" t="str">
         <f>_xlfn.XLOOKUP(A47,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Red Bull Racing-Red Bull Ford</v>
       </c>
-      <c r="D47" s="24" t="str">
+      <c r="D47" s="23" t="str">
         <f>_xlfn.XLOOKUP(A47,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Austria Oracle Red Bull Racing</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="20" t="s">
+      <c r="E47" s="26" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A48" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="B48" s="26" cm="1">
+      <c r="B48" s="25" cm="1">
         <f t="array" ref="B48">_xlfn._xlws.FILTER(Drivers!D:D,Drivers!B:B=Table6[[#This Row],[Driver]],0)</f>
         <v>6</v>
       </c>
-      <c r="C48" s="24" t="str">
+      <c r="C48" s="23" t="str">
         <f>_xlfn.XLOOKUP(A48,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Red Bull Racing-Red Bull Ford</v>
       </c>
-      <c r="D48" s="24" t="str">
+      <c r="D48" s="23" t="str">
         <f>_xlfn.XLOOKUP(A48,Constructor!$C$2:$C$23,Constructor!$A$2:$A$23,"")</f>
         <v>Austria Oracle Red Bull Racing</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -7381,11 +7575,11 @@
     <col min="28" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="129" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:27" ht="130.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>13</v>
       </c>
       <c r="C1" s="5" t="s">
@@ -7463,199 +7657,199 @@
       <c r="AA1" s="6"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="24" t="str">
+      <c r="B2" s="23" t="str">
         <f>_xlfn.XLOOKUP(A2,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Alpine-Mercedes</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="24" t="str">
+      <c r="B3" s="23" t="str">
         <f>_xlfn.XLOOKUP(A3,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Alpine-Mercedes</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="24" t="str">
+      <c r="B4" s="23" t="str">
         <f>_xlfn.XLOOKUP(A4,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Aston Martin Aramco-Honda</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="24" t="str">
+      <c r="B5" s="23" t="str">
         <f>_xlfn.XLOOKUP(A5,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Aston Martin Aramco-Honda</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="24" t="str">
+      <c r="B6" s="23" t="str">
         <f>_xlfn.XLOOKUP(A6,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Atlassian Williams-Mercedes</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="24" t="str">
+      <c r="B7" s="23" t="str">
         <f>_xlfn.XLOOKUP(A7,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Atlassian Williams-Mercedes</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="24" t="str">
+      <c r="B8" s="23" t="str">
         <f>_xlfn.XLOOKUP(A8,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Audi</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="24" t="str">
+      <c r="B9" s="23" t="str">
         <f>_xlfn.XLOOKUP(A9,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Audi</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="24" t="str">
+      <c r="B10" s="23" t="str">
         <f>_xlfn.XLOOKUP(A10,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Cadillac-Ferrari</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="24" t="str">
+      <c r="B11" s="23" t="str">
         <f>_xlfn.XLOOKUP(A11,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Cadillac-Ferrari</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="24" t="str">
+      <c r="B12" s="23" t="str">
         <f>_xlfn.XLOOKUP(A12,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Ferrari</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="24" t="str">
+      <c r="B13" s="23" t="str">
         <f>_xlfn.XLOOKUP(A13,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Ferrari</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="24" t="str">
+      <c r="B14" s="23" t="str">
         <f>_xlfn.XLOOKUP(A14,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Haas-Ferrari</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="24" t="str">
+      <c r="B15" s="23" t="str">
         <f>_xlfn.XLOOKUP(A15,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Haas-Ferrari</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="24" t="str">
+      <c r="B16" s="23" t="str">
         <f>_xlfn.XLOOKUP(A16,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>McLaren-Mercedes</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="24" t="str">
+      <c r="B17" s="23" t="str">
         <f>_xlfn.XLOOKUP(A17,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>McLaren-Mercedes</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="B18" s="24" t="str">
+      <c r="B18" s="23" t="str">
         <f>_xlfn.XLOOKUP(A18,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Mercedes</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="24" t="str">
+      <c r="B19" s="23" t="str">
         <f>_xlfn.XLOOKUP(A19,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Mercedes</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="24" t="str">
+      <c r="B20" s="23" t="str">
         <f>_xlfn.XLOOKUP(A20,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Racing Bulls-Red Bull Ford</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="B21" s="24" t="str">
+      <c r="B21" s="23" t="str">
         <f>_xlfn.XLOOKUP(A21,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Racing Bulls-Red Bull Ford</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="24" t="str">
+      <c r="B22" s="23" t="str">
         <f>_xlfn.XLOOKUP(A22,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Red Bull Racing-Red Bull Ford</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="24" t="str">
+      <c r="B23" s="23" t="str">
         <f>_xlfn.XLOOKUP(A23,Constructor!$C$2:$C$23,Constructor!$B$2:$B$23,"")</f>
         <v>Red Bull Racing-Red Bull Ford</v>
       </c>
@@ -7702,12 +7896,12 @@
       <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
     </row>
@@ -7720,21 +7914,21 @@
         <f>_xlfn.XLOOKUP(C2,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Alpine-Mercedes</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
     </row>
@@ -7747,21 +7941,21 @@
         <f>_xlfn.XLOOKUP(C3,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Alpine-Mercedes</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
     </row>
@@ -7774,21 +7968,21 @@
         <f>_xlfn.XLOOKUP(C4,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Aston Martin Aramco-Honda</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
     </row>
@@ -7801,21 +7995,21 @@
         <f>_xlfn.XLOOKUP(C5,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Aston Martin Aramco-Honda</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
     </row>
@@ -7828,21 +8022,21 @@
         <f>_xlfn.XLOOKUP(C6,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Atlassian Williams-Mercedes</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
     </row>
@@ -7855,21 +8049,21 @@
         <f>_xlfn.XLOOKUP(C7,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Atlassian Williams-Mercedes</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
     </row>
@@ -7882,21 +8076,21 @@
         <f>_xlfn.XLOOKUP(C8,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Audi</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
     </row>
@@ -7909,21 +8103,21 @@
         <f>_xlfn.XLOOKUP(C9,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Audi</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
     </row>
@@ -7936,21 +8130,21 @@
         <f>_xlfn.XLOOKUP(C10,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Cadillac-Ferrari</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
     </row>
@@ -7963,21 +8157,21 @@
         <f>_xlfn.XLOOKUP(C11,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Cadillac-Ferrari</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
     </row>
@@ -7990,21 +8184,21 @@
         <f>_xlfn.XLOOKUP(C12,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Ferrari</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
     </row>
@@ -8017,21 +8211,21 @@
         <f>_xlfn.XLOOKUP(C13,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Ferrari</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="20"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
     </row>
@@ -8044,21 +8238,21 @@
         <f>_xlfn.XLOOKUP(C14,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Haas-Ferrari</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
     </row>
@@ -8071,21 +8265,21 @@
         <f>_xlfn.XLOOKUP(C15,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Haas-Ferrari</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
     </row>
@@ -8098,21 +8292,21 @@
         <f>_xlfn.XLOOKUP(C16,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>McLaren-Mercedes</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="19"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
     </row>
@@ -8125,21 +8319,21 @@
         <f>_xlfn.XLOOKUP(C17,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>McLaren-Mercedes</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
     </row>
@@ -8152,21 +8346,21 @@
         <f>_xlfn.XLOOKUP(C18,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Mercedes</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
     </row>
@@ -8179,21 +8373,21 @@
         <f>_xlfn.XLOOKUP(C19,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Mercedes</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="G19" s="20"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
     </row>
@@ -8206,21 +8400,21 @@
         <f>_xlfn.XLOOKUP(C20,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Racing Bulls-Red Bull Ford</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
     </row>
@@ -8233,21 +8427,21 @@
         <f>_xlfn.XLOOKUP(C21,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Racing Bulls-Red Bull Ford</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
     </row>
@@ -8260,21 +8454,21 @@
         <f>_xlfn.XLOOKUP(C22,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Red Bull Racing-Red Bull Ford</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
     </row>
@@ -8287,105 +8481,105 @@
         <f>_xlfn.XLOOKUP(C23,Drivers!$B$2:$B$23,Drivers!$F$2:$F$23,"")</f>
         <v>Red Bull Racing-Red Bull Ford</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G28" s="20"/>
+      <c r="G28" s="19"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G29" s="20"/>
+      <c r="G29" s="19"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G30" s="20"/>
+      <c r="G30" s="19"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G31" s="20"/>
+      <c r="G31" s="19"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="G32" s="20"/>
+      <c r="G32" s="19"/>
     </row>
     <row r="33" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G33" s="20"/>
+      <c r="G33" s="19"/>
     </row>
     <row r="34" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G34" s="20"/>
+      <c r="G34" s="19"/>
     </row>
     <row r="35" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G35" s="20"/>
+      <c r="G35" s="19"/>
     </row>
     <row r="36" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G36" s="20"/>
+      <c r="G36" s="19"/>
     </row>
     <row r="37" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G37" s="20"/>
+      <c r="G37" s="19"/>
     </row>
     <row r="38" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G38" s="20"/>
+      <c r="G38" s="19"/>
     </row>
     <row r="39" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G39" s="20"/>
+      <c r="G39" s="19"/>
     </row>
     <row r="40" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G40" s="20"/>
+      <c r="G40" s="19"/>
     </row>
     <row r="41" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G41" s="20"/>
+      <c r="G41" s="19"/>
     </row>
     <row r="42" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G42" s="20"/>
+      <c r="G42" s="19"/>
     </row>
     <row r="43" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G43" s="20"/>
+      <c r="G43" s="19"/>
     </row>
     <row r="44" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G44" s="20"/>
+      <c r="G44" s="19"/>
     </row>
     <row r="45" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G45" s="20"/>
+      <c r="G45" s="19"/>
     </row>
     <row r="46" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G46" s="20"/>
+      <c r="G46" s="19"/>
     </row>
     <row r="47" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G47" s="20"/>
+      <c r="G47" s="19"/>
     </row>
     <row r="48" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G48" s="20"/>
+      <c r="G48" s="19"/>
     </row>
     <row r="49" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G49" s="20"/>
+      <c r="G49" s="19"/>
     </row>
     <row r="50" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G50" s="20"/>
+      <c r="G50" s="19"/>
     </row>
     <row r="51" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G51" s="20"/>
+      <c r="G51" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
